--- a/test-case-exports/Topup.xlsx
+++ b/test-case-exports/Topup.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="709" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="969" uniqueCount="152">
   <si>
     <t>#</t>
   </si>
@@ -62,7 +62,7 @@
     <t>Yes</t>
   </si>
   <si>
-    <t>test.skip(true, ...) in body — pending Admin Portal "Commission Management" automation (EMI-2031)</t>
+    <t>Skipped: pending Admin Portal "Commission Management" automation (EMI-2031)</t>
   </si>
   <si>
     <t>TU-CM02 — custom per-account schema overrides the default</t>
@@ -122,30 +122,81 @@
     <t>Topup — Card Payment Flow</t>
   </si>
   <si>
-    <t>data.testName</t>
+    <t>Topup_with_Enter_Amount_MADA</t>
   </si>
   <si>
     <t>Active</t>
   </si>
   <si>
+    <t>Topup_with_Enter_Amount_VISA</t>
+  </si>
+  <si>
+    <t>Topup_with_Enter_Amount_MASTER</t>
+  </si>
+  <si>
+    <t>Topup_with_Select_Amount_VISA</t>
+  </si>
+  <si>
+    <t>Topup_with_Valid_TwoDecimal_Amount_VISA</t>
+  </si>
+  <si>
+    <t>Topup_with_Invalid_Card_Data_PayNowDisabled</t>
+  </si>
+  <si>
+    <t>Topup_Failed_User_Canceled|From_The_HyperPay_Screen</t>
+  </si>
+  <si>
+    <t>Topup_Failed_Limit_Exceeded|From_The_HyperPay_Screen</t>
+  </si>
+  <si>
+    <t>Topup_Failed_Too_Many_Tries|From_The_HyperPay_Screen</t>
+  </si>
+  <si>
+    <t>Topup_Pending_Simulation|From_The_HyperPay_Screen</t>
+  </si>
+  <si>
+    <t>Topup_verifyAmountField_PreventsInvalidInput</t>
+  </si>
+  <si>
+    <t>Topup_verifyAmountField_PreventsZeroAmount</t>
+  </si>
+  <si>
+    <t>Topup_verifyAmountField_PreventsInvalidChars</t>
+  </si>
+  <si>
+    <t>Topup_AmountValidation_ValidFloat_2_Decimals</t>
+  </si>
+  <si>
+    <t>Topup_AmountValidation_ValidFloat_1_Decimal</t>
+  </si>
+  <si>
+    <t>Topup_AmountValidation_InvalidFloat_3_Decimals</t>
+  </si>
+  <si>
+    <t>Topup_AmountValidation_CopyPaste_Valid</t>
+  </si>
+  <si>
+    <t>Topup_AmountValidation_CopyPaste_Invalid</t>
+  </si>
+  <si>
+    <t>Topup_CancelTransaction_PageRefresh</t>
+  </si>
+  <si>
+    <t>Topup_CancelTransaction_SummaryCancelButton</t>
+  </si>
+  <si>
+    <t>BusinessTestCases/Topup/functional/TopupSadadFlow.spec.ts</t>
+  </si>
+  <si>
+    <t>Topup — SADAD Bill Generation (TU-09, TU-10)</t>
+  </si>
+  <si>
+    <t>TU-09: should generate a SADAD top-up bill with reference, amount, and expiry</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>dynamic title (template literal)</t>
-  </si>
-  <si>
-    <t>BusinessTestCases/Topup/functional/TopupSadadFlow.spec.ts</t>
-  </si>
-  <si>
-    <t>Topup — SADAD Bill Generation (TU-09, TU-10)</t>
-  </si>
-  <si>
-    <t>TU-09: should generate a SADAD top-up bill with reference, amount, and expiry</t>
-  </si>
-  <si>
-    <t>route mocking</t>
-  </si>
-  <si>
     <t>TU-10: should offer download or copy-reference actions on a generated bill</t>
   </si>
   <si>
@@ -170,7 +221,7 @@
     <t>TU-TL01 — top-ups within the daily amount limit succeed (App)</t>
   </si>
   <si>
-    <t>test.skip(true, ...) in body — pending Admin Portal "Manage Limits → Transaction" automation (EMI-87/EMI-1653/EMI-195)</t>
+    <t>Skipped: pending Admin Portal "Manage Limits → Transaction" automation (EMI-87/EMI-1653/EMI-195)</t>
   </si>
   <si>
     <t>TU-TL02 — cumulative top-ups exceeding the daily amount limit are blocked (App)</t>
@@ -215,7 +266,7 @@
     <t>TU-WB01 — top-up within max-balance ceiling succeeds (Merchant, Low risk)</t>
   </si>
   <si>
-    <t>test.skip(true, ...) in body — pending Admin Portal "Manage Limits → Wallet Balance" automation (EMI-1653/EMI-195)</t>
+    <t>Skipped: pending Admin Portal "Manage Limits → Wallet Balance" automation (EMI-1653/EMI-195)</t>
   </si>
   <si>
     <t>TU-WB02 — top-up breaching max-balance ceiling is blocked (Merchant, Low risk)</t>
@@ -245,7 +296,7 @@
     <t>Topup – Page Elements</t>
   </si>
   <si>
-    <t>reached via ${entry.name}</t>
+    <t>reached via home page quick action</t>
   </si>
   <si>
     <t>should display the "Top up" page title and its description</t>
@@ -284,6 +335,9 @@
     <t>should display the Proceed button with its arrow icon</t>
   </si>
   <si>
+    <t>reached via side menu link</t>
+  </si>
+  <si>
     <t>BusinessTestCases/Topup/ui/TopupSummaryPage.spec.ts</t>
   </si>
   <si>
@@ -338,6 +392,24 @@
     <t>should display the profile dropdown trigger</t>
   </si>
   <si>
+    <t>should display the "Top Up Summary" heading and its subtext</t>
+  </si>
+  <si>
+    <t>should display the Current balance label and value</t>
+  </si>
+  <si>
+    <t>should display the generate QR Code and wallet settings buttons</t>
+  </si>
+  <si>
+    <t>should display the Transaction Type and Payment Method rows</t>
+  </si>
+  <si>
+    <t>should display the Original Amount, Commission, VAT, and Total amount rows</t>
+  </si>
+  <si>
+    <t>should display the Cancel and Next buttons</t>
+  </si>
+  <si>
     <t>profile dropdown</t>
   </si>
   <si>
@@ -365,37 +437,19 @@
     <t>should display the Sign out button</t>
   </si>
   <si>
-    <t>should display the "Top Up Summary" heading and its subtext</t>
-  </si>
-  <si>
-    <t>should display the Current balance label and value</t>
-  </si>
-  <si>
-    <t>should display the generate QR Code and wallet settings buttons</t>
-  </si>
-  <si>
-    <t>should display the Transaction Type and Payment Method rows</t>
-  </si>
-  <si>
-    <t>should display the Original Amount, Commission, VAT, and Total amount rows</t>
-  </si>
-  <si>
-    <t>should display the Cancel and Next buttons</t>
-  </si>
-  <si>
     <t>Summary — Topup</t>
   </si>
   <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-26T17:32:41.410Z</t>
+    <t>2026-09-08T15:08:53.779Z</t>
   </si>
   <si>
     <t>Total test cases</t>
   </si>
   <si>
-    <t>Count per sub-folder (ui / functional / api / archive)</t>
+    <t>Count per sub-folder</t>
   </si>
   <si>
     <t>functional</t>
@@ -410,7 +464,10 @@
     <t>Archived</t>
   </si>
   <si>
-    <t>Spec files in this module</t>
+    <t>Gated behind an env flag</t>
+  </si>
+  <si>
+    <t>Spec files</t>
   </si>
 </sst>
 </file>
@@ -428,6 +485,7 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b/>
@@ -437,7 +495,7 @@
       <b/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -447,11 +505,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
       </patternFill>
     </fill>
   </fills>
@@ -469,8 +522,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -812,19 +869,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I118"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="60" customWidth="1"/>
-    <col min="4" max="4" width="46" customWidth="1"/>
-    <col min="5" max="5" width="27" customWidth="1"/>
-    <col min="6" max="6" width="60" customWidth="1"/>
-    <col min="7" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="60" customWidth="1"/>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="22" customWidth="1"/>
+    <col min="3" max="3" width="58" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="62" customWidth="1"/>
+    <col min="7" max="7" width="12" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="48" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="24" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -853,36 +912,36 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2">
+    <row r="2" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
+      <c r="B2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
@@ -911,36 +970,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4">
+    <row r="4" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E4" t="s">
-        <v>12</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H4" t="s">
-        <v>15</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="H4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
@@ -969,36 +1028,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6">
+    <row r="6" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="B6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="G6" t="s">
+      <c r="G6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H6" t="s">
-        <v>15</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="H6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>6</v>
       </c>
@@ -1027,36 +1086,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A8">
+    <row r="8" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" t="s">
+      <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" t="s">
+      <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G8" t="s">
+      <c r="G8" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H8" t="s">
-        <v>15</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="H8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <v>8</v>
       </c>
@@ -1085,36 +1144,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" t="s">
+    <row r="10" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E10" t="s">
-        <v>12</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="E10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="G10" t="s">
+      <c r="G10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H10" t="s">
-        <v>15</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="H10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>10</v>
       </c>
@@ -1143,36 +1202,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12">
+    <row r="12" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E12" t="s">
-        <v>12</v>
-      </c>
-      <c r="F12" t="s">
+      <c r="E12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="G12" t="s">
+      <c r="G12" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H12" t="s">
-        <v>15</v>
-      </c>
-      <c r="I12" t="s">
+      <c r="H12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <v>12</v>
       </c>
@@ -1201,36 +1260,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A14">
+    <row r="14" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E14" t="s">
-        <v>12</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="E14" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="G14" t="s">
+      <c r="G14" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H14" t="s">
-        <v>15</v>
-      </c>
-      <c r="I14" t="s">
+      <c r="H14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <v>14</v>
       </c>
@@ -1259,36 +1318,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C16" t="s">
+    <row r="16" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E16" t="s">
-        <v>12</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="E16" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="G16" t="s">
+      <c r="G16" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H16" t="s">
-        <v>15</v>
-      </c>
-      <c r="I16" t="s">
+      <c r="H16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>16</v>
       </c>
@@ -1317,36 +1376,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18">
+    <row r="18" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="B18" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D18" t="s">
+      <c r="D18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="E18" t="s">
-        <v>12</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="E18" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G18" t="s">
+      <c r="G18" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H18" t="s">
-        <v>15</v>
-      </c>
-      <c r="I18" t="s">
+      <c r="H18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>18</v>
       </c>
@@ -1375,36 +1434,36 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20">
+    <row r="20" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" t="s">
+      <c r="B20" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D20" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E20" t="s">
-        <v>12</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="E20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="G20" t="s">
-        <v>37</v>
-      </c>
-      <c r="H20" t="s">
-        <v>38</v>
-      </c>
-      <c r="I20" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <v>20</v>
       </c>
@@ -1412,57 +1471,57 @@
         <v>9</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>37</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A22">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" t="s">
-        <v>40</v>
-      </c>
-      <c r="D22" t="s">
-        <v>41</v>
-      </c>
-      <c r="E22" t="s">
-        <v>12</v>
-      </c>
-      <c r="F22" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" t="s">
-        <v>37</v>
-      </c>
-      <c r="H22" t="s">
-        <v>38</v>
-      </c>
-      <c r="I22" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>22</v>
       </c>
@@ -1470,57 +1529,57 @@
         <v>9</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="G23" s="2" t="s">
         <v>37</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" t="s">
-        <v>9</v>
-      </c>
-      <c r="C24" t="s">
-        <v>40</v>
-      </c>
-      <c r="D24" t="s">
-        <v>47</v>
-      </c>
-      <c r="E24" t="s">
-        <v>12</v>
-      </c>
-      <c r="F24" t="s">
-        <v>48</v>
-      </c>
-      <c r="G24" t="s">
-        <v>37</v>
-      </c>
-      <c r="H24" t="s">
-        <v>38</v>
-      </c>
-      <c r="I24" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B24" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>24</v>
       </c>
@@ -1528,57 +1587,57 @@
         <v>9</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A26">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" t="s">
-        <v>12</v>
-      </c>
-      <c r="F26" t="s">
-        <v>53</v>
-      </c>
-      <c r="G26" t="s">
-        <v>14</v>
-      </c>
-      <c r="H26" t="s">
-        <v>15</v>
-      </c>
-      <c r="I26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B26" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <v>26</v>
       </c>
@@ -1586,57 +1645,57 @@
         <v>9</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A28">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" t="s">
-        <v>50</v>
-      </c>
-      <c r="E28" t="s">
-        <v>12</v>
-      </c>
-      <c r="F28" t="s">
-        <v>55</v>
-      </c>
-      <c r="G28" t="s">
-        <v>14</v>
-      </c>
-      <c r="H28" t="s">
-        <v>15</v>
-      </c>
-      <c r="I28" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B28" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <v>28</v>
       </c>
@@ -1644,57 +1703,57 @@
         <v>9</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30" t="s">
-        <v>12</v>
-      </c>
-      <c r="F30" t="s">
-        <v>57</v>
-      </c>
-      <c r="G30" t="s">
-        <v>14</v>
-      </c>
-      <c r="H30" t="s">
-        <v>15</v>
-      </c>
-      <c r="I30" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B30" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <v>30</v>
       </c>
@@ -1702,57 +1761,57 @@
         <v>9</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <v>31</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32" t="s">
-        <v>12</v>
-      </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
-      <c r="G32" t="s">
-        <v>14</v>
-      </c>
-      <c r="H32" t="s">
-        <v>15</v>
-      </c>
-      <c r="I32" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G32" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <v>32</v>
       </c>
@@ -1760,57 +1819,57 @@
         <v>9</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F33" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="G33" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" t="s">
-        <v>12</v>
-      </c>
-      <c r="F34" t="s">
-        <v>61</v>
-      </c>
-      <c r="G34" t="s">
-        <v>14</v>
-      </c>
-      <c r="H34" t="s">
-        <v>15</v>
-      </c>
-      <c r="I34" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B34" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <v>34</v>
       </c>
@@ -1818,57 +1877,57 @@
         <v>9</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" t="s">
-        <v>49</v>
-      </c>
-      <c r="D36" t="s">
-        <v>50</v>
-      </c>
-      <c r="E36" t="s">
-        <v>12</v>
-      </c>
-      <c r="F36" t="s">
-        <v>63</v>
-      </c>
-      <c r="G36" t="s">
-        <v>14</v>
-      </c>
-      <c r="H36" t="s">
-        <v>15</v>
-      </c>
-      <c r="I36" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B36" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <v>36</v>
       </c>
@@ -1876,57 +1935,57 @@
         <v>9</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" t="s">
-        <v>64</v>
-      </c>
-      <c r="D38" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38" t="s">
-        <v>12</v>
-      </c>
-      <c r="F38" t="s">
-        <v>68</v>
-      </c>
-      <c r="G38" t="s">
-        <v>14</v>
-      </c>
-      <c r="H38" t="s">
-        <v>15</v>
-      </c>
-      <c r="I38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <v>38</v>
       </c>
@@ -1934,57 +1993,57 @@
         <v>9</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>64</v>
+        <v>34</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="E39" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A40">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" t="s">
-        <v>64</v>
-      </c>
-      <c r="D40" t="s">
-        <v>65</v>
-      </c>
-      <c r="E40" t="s">
-        <v>12</v>
-      </c>
-      <c r="F40" t="s">
-        <v>70</v>
-      </c>
-      <c r="G40" t="s">
-        <v>14</v>
-      </c>
-      <c r="H40" t="s">
-        <v>15</v>
-      </c>
-      <c r="I40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <v>40</v>
       </c>
@@ -1992,57 +2051,57 @@
         <v>9</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="I41" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A42">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
         <v>41</v>
       </c>
-      <c r="B42" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" t="s">
-        <v>64</v>
-      </c>
-      <c r="D42" t="s">
-        <v>65</v>
-      </c>
-      <c r="E42" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" t="s">
-        <v>72</v>
-      </c>
-      <c r="G42" t="s">
-        <v>14</v>
-      </c>
-      <c r="H42" t="s">
-        <v>15</v>
-      </c>
-      <c r="I42" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B42" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <v>42</v>
       </c>
@@ -2050,57 +2109,57 @@
         <v>9</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F43" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F43" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="G43" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <v>43</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="G44" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="H43" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" t="s">
-        <v>64</v>
-      </c>
-      <c r="D44" t="s">
-        <v>65</v>
-      </c>
-      <c r="E44" t="s">
-        <v>12</v>
-      </c>
-      <c r="F44" t="s">
-        <v>74</v>
-      </c>
-      <c r="G44" t="s">
-        <v>14</v>
-      </c>
-      <c r="H44" t="s">
-        <v>15</v>
-      </c>
-      <c r="I44" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H44" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <v>44</v>
       </c>
@@ -2108,57 +2167,57 @@
         <v>9</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A46">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
         <v>45</v>
       </c>
-      <c r="B46" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" t="s">
-        <v>75</v>
-      </c>
-      <c r="D46" t="s">
-        <v>76</v>
-      </c>
-      <c r="E46" t="s">
-        <v>77</v>
-      </c>
-      <c r="F46" t="s">
-        <v>79</v>
-      </c>
-      <c r="G46" t="s">
-        <v>37</v>
-      </c>
-      <c r="H46" t="s">
-        <v>15</v>
-      </c>
-      <c r="I46" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B46" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <v>46</v>
       </c>
@@ -2166,57 +2225,57 @@
         <v>9</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A48">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
         <v>47</v>
       </c>
-      <c r="B48" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" t="s">
-        <v>75</v>
-      </c>
-      <c r="D48" t="s">
-        <v>76</v>
-      </c>
-      <c r="E48" t="s">
-        <v>77</v>
-      </c>
-      <c r="F48" t="s">
-        <v>81</v>
-      </c>
-      <c r="G48" t="s">
-        <v>37</v>
-      </c>
-      <c r="H48" t="s">
-        <v>15</v>
-      </c>
-      <c r="I48" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <v>48</v>
       </c>
@@ -2224,57 +2283,57 @@
         <v>9</v>
       </c>
       <c r="C49" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <v>49</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F50" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D49" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F49" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" t="s">
-        <v>75</v>
-      </c>
-      <c r="D50" t="s">
-        <v>76</v>
-      </c>
-      <c r="E50" t="s">
-        <v>77</v>
-      </c>
-      <c r="F50" t="s">
-        <v>83</v>
-      </c>
-      <c r="G50" t="s">
-        <v>37</v>
-      </c>
-      <c r="H50" t="s">
-        <v>15</v>
-      </c>
-      <c r="I50" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <v>50</v>
       </c>
@@ -2282,57 +2341,57 @@
         <v>9</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="G51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F52" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="F51" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G51" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H51" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" t="s">
-        <v>75</v>
-      </c>
-      <c r="D52" t="s">
-        <v>76</v>
-      </c>
-      <c r="E52" t="s">
-        <v>77</v>
-      </c>
-      <c r="F52" t="s">
-        <v>85</v>
-      </c>
-      <c r="G52" t="s">
-        <v>37</v>
-      </c>
-      <c r="H52" t="s">
-        <v>15</v>
-      </c>
-      <c r="I52" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2340,57 +2399,57 @@
         <v>9</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A54">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" t="s">
-        <v>75</v>
-      </c>
-      <c r="D54" t="s">
-        <v>76</v>
-      </c>
-      <c r="E54" t="s">
-        <v>77</v>
-      </c>
-      <c r="F54" t="s">
-        <v>87</v>
-      </c>
-      <c r="G54" t="s">
-        <v>37</v>
-      </c>
-      <c r="H54" t="s">
-        <v>15</v>
-      </c>
-      <c r="I54" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2398,57 +2457,57 @@
         <v>9</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>77</v>
+        <v>12</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A56">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" t="s">
-        <v>75</v>
-      </c>
-      <c r="D56" t="s">
-        <v>76</v>
-      </c>
-      <c r="E56" t="s">
-        <v>77</v>
-      </c>
-      <c r="F56" t="s">
-        <v>89</v>
-      </c>
-      <c r="G56" t="s">
-        <v>37</v>
-      </c>
-      <c r="H56" t="s">
-        <v>15</v>
-      </c>
-      <c r="I56" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B56" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2456,57 +2515,57 @@
         <v>9</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A58">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" t="s">
-        <v>90</v>
-      </c>
-      <c r="D58" t="s">
-        <v>91</v>
-      </c>
-      <c r="E58" t="s">
-        <v>12</v>
-      </c>
-      <c r="F58" t="s">
-        <v>93</v>
-      </c>
-      <c r="G58" t="s">
-        <v>37</v>
-      </c>
-      <c r="H58" t="s">
-        <v>15</v>
-      </c>
-      <c r="I58" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B58" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2514,57 +2573,57 @@
         <v>9</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>12</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>94</v>
+        <v>87</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A60">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" t="s">
-        <v>9</v>
-      </c>
-      <c r="C60" t="s">
-        <v>90</v>
-      </c>
-      <c r="D60" t="s">
-        <v>91</v>
-      </c>
-      <c r="E60" t="s">
-        <v>12</v>
-      </c>
-      <c r="F60" t="s">
-        <v>95</v>
-      </c>
-      <c r="G60" t="s">
-        <v>37</v>
-      </c>
-      <c r="H60" t="s">
-        <v>15</v>
-      </c>
-      <c r="I60" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B60" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2572,57 +2631,57 @@
         <v>9</v>
       </c>
       <c r="C61" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F62" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D61" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="E61" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F61" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H61" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A62">
-        <v>61</v>
-      </c>
-      <c r="B62" t="s">
-        <v>9</v>
-      </c>
-      <c r="C62" t="s">
-        <v>90</v>
-      </c>
-      <c r="D62" t="s">
-        <v>91</v>
-      </c>
-      <c r="E62" t="s">
-        <v>12</v>
-      </c>
-      <c r="F62" t="s">
-        <v>97</v>
-      </c>
-      <c r="G62" t="s">
-        <v>37</v>
-      </c>
-      <c r="H62" t="s">
-        <v>15</v>
-      </c>
-      <c r="I62" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="G62" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H62" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2630,57 +2689,57 @@
         <v>9</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F63" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F63" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="G63" s="2" t="s">
-        <v>37</v>
+        <v>14</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A64">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="2">
         <v>63</v>
       </c>
-      <c r="B64" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" t="s">
-        <v>90</v>
-      </c>
-      <c r="D64" t="s">
-        <v>91</v>
-      </c>
-      <c r="E64" t="s">
-        <v>12</v>
-      </c>
-      <c r="F64" t="s">
-        <v>99</v>
-      </c>
-      <c r="G64" t="s">
-        <v>37</v>
-      </c>
-      <c r="H64" t="s">
-        <v>15</v>
-      </c>
-      <c r="I64" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B64" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H64" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2">
         <v>64</v>
       </c>
@@ -2688,16 +2747,16 @@
         <v>9</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>37</v>
@@ -2709,36 +2768,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A66">
+    <row r="66" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="2">
         <v>65</v>
       </c>
-      <c r="B66" t="s">
-        <v>9</v>
-      </c>
-      <c r="C66" t="s">
-        <v>90</v>
-      </c>
-      <c r="D66" t="s">
-        <v>91</v>
-      </c>
-      <c r="E66" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" t="s">
-        <v>101</v>
-      </c>
-      <c r="G66" t="s">
-        <v>37</v>
-      </c>
-      <c r="H66" t="s">
-        <v>15</v>
-      </c>
-      <c r="I66" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B66" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2">
         <v>66</v>
       </c>
@@ -2746,16 +2805,16 @@
         <v>9</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>37</v>
@@ -2767,36 +2826,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A68">
+    <row r="68" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="2">
         <v>67</v>
       </c>
-      <c r="B68" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" t="s">
-        <v>90</v>
-      </c>
-      <c r="D68" t="s">
-        <v>91</v>
-      </c>
-      <c r="E68" t="s">
-        <v>12</v>
-      </c>
-      <c r="F68" t="s">
-        <v>103</v>
-      </c>
-      <c r="G68" t="s">
-        <v>37</v>
-      </c>
-      <c r="H68" t="s">
-        <v>15</v>
-      </c>
-      <c r="I68" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B68" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H68" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I68" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2">
         <v>68</v>
       </c>
@@ -2804,16 +2863,16 @@
         <v>9</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>37</v>
@@ -2825,36 +2884,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A70">
+    <row r="70" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="2">
         <v>69</v>
       </c>
-      <c r="B70" t="s">
-        <v>9</v>
-      </c>
-      <c r="C70" t="s">
-        <v>90</v>
-      </c>
-      <c r="D70" t="s">
-        <v>91</v>
-      </c>
-      <c r="E70" t="s">
-        <v>12</v>
-      </c>
-      <c r="F70" t="s">
-        <v>105</v>
-      </c>
-      <c r="G70" t="s">
-        <v>37</v>
-      </c>
-      <c r="H70" t="s">
-        <v>15</v>
-      </c>
-      <c r="I70" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B70" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2">
         <v>70</v>
       </c>
@@ -2862,16 +2921,16 @@
         <v>9</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>37</v>
@@ -2883,36 +2942,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A72">
+    <row r="72" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="2">
         <v>71</v>
       </c>
-      <c r="B72" t="s">
-        <v>9</v>
-      </c>
-      <c r="C72" t="s">
-        <v>90</v>
-      </c>
-      <c r="D72" t="s">
-        <v>91</v>
-      </c>
-      <c r="E72" t="s">
-        <v>12</v>
-      </c>
-      <c r="F72" t="s">
-        <v>107</v>
-      </c>
-      <c r="G72" t="s">
-        <v>37</v>
-      </c>
-      <c r="H72" t="s">
-        <v>15</v>
-      </c>
-      <c r="I72" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B72" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H72" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I72" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2">
         <v>72</v>
       </c>
@@ -2920,16 +2979,16 @@
         <v>9</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>37</v>
@@ -2941,36 +3000,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A74">
+    <row r="74" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="2">
         <v>73</v>
       </c>
-      <c r="B74" t="s">
-        <v>9</v>
-      </c>
-      <c r="C74" t="s">
-        <v>90</v>
-      </c>
-      <c r="D74" t="s">
-        <v>91</v>
-      </c>
-      <c r="E74" t="s">
-        <v>108</v>
-      </c>
-      <c r="F74" t="s">
-        <v>110</v>
-      </c>
-      <c r="G74" t="s">
-        <v>37</v>
-      </c>
-      <c r="H74" t="s">
-        <v>15</v>
-      </c>
-      <c r="I74" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B74" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H74" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I74" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2">
         <v>74</v>
       </c>
@@ -2978,16 +3037,16 @@
         <v>9</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>108</v>
+        <v>94</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>37</v>
@@ -2999,36 +3058,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A76">
+    <row r="76" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="2">
         <v>75</v>
       </c>
-      <c r="B76" t="s">
-        <v>9</v>
-      </c>
-      <c r="C76" t="s">
-        <v>90</v>
-      </c>
-      <c r="D76" t="s">
-        <v>91</v>
-      </c>
-      <c r="E76" t="s">
-        <v>108</v>
-      </c>
-      <c r="F76" t="s">
-        <v>112</v>
-      </c>
-      <c r="G76" t="s">
-        <v>37</v>
-      </c>
-      <c r="H76" t="s">
-        <v>15</v>
-      </c>
-      <c r="I76" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B76" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H76" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I76" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2">
         <v>76</v>
       </c>
@@ -3036,16 +3095,16 @@
         <v>9</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>37</v>
@@ -3057,36 +3116,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A78">
+    <row r="78" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="2">
         <v>77</v>
       </c>
-      <c r="B78" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" t="s">
-        <v>90</v>
-      </c>
-      <c r="D78" t="s">
-        <v>91</v>
-      </c>
-      <c r="E78" t="s">
-        <v>108</v>
-      </c>
-      <c r="F78" t="s">
-        <v>114</v>
-      </c>
-      <c r="G78" t="s">
-        <v>37</v>
-      </c>
-      <c r="H78" t="s">
-        <v>15</v>
-      </c>
-      <c r="I78" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B78" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H78" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I78" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
         <v>78</v>
       </c>
@@ -3094,16 +3153,16 @@
         <v>9</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>37</v>
@@ -3115,36 +3174,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A80">
+    <row r="80" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="2">
         <v>79</v>
       </c>
-      <c r="B80" t="s">
-        <v>9</v>
-      </c>
-      <c r="C80" t="s">
-        <v>90</v>
-      </c>
-      <c r="D80" t="s">
-        <v>91</v>
-      </c>
-      <c r="E80" t="s">
-        <v>108</v>
-      </c>
-      <c r="F80" t="s">
-        <v>116</v>
-      </c>
-      <c r="G80" t="s">
-        <v>37</v>
-      </c>
-      <c r="H80" t="s">
-        <v>15</v>
-      </c>
-      <c r="I80" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B80" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I80" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
         <v>80</v>
       </c>
@@ -3152,16 +3211,16 @@
         <v>9</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>37</v>
@@ -3173,36 +3232,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A82">
+    <row r="82" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="2">
         <v>81</v>
       </c>
-      <c r="B82" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" t="s">
-        <v>90</v>
-      </c>
-      <c r="D82" t="s">
-        <v>91</v>
-      </c>
-      <c r="E82" t="s">
-        <v>12</v>
-      </c>
-      <c r="F82" t="s">
-        <v>118</v>
-      </c>
-      <c r="G82" t="s">
-        <v>37</v>
-      </c>
-      <c r="H82" t="s">
-        <v>15</v>
-      </c>
-      <c r="I82" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B82" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I82" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
         <v>82</v>
       </c>
@@ -3210,16 +3269,16 @@
         <v>9</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>80</v>
+        <v>102</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>37</v>
@@ -3231,36 +3290,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A84">
+    <row r="84" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="2">
         <v>83</v>
       </c>
-      <c r="B84" t="s">
-        <v>9</v>
-      </c>
-      <c r="C84" t="s">
-        <v>90</v>
-      </c>
-      <c r="D84" t="s">
-        <v>91</v>
-      </c>
-      <c r="E84" t="s">
-        <v>12</v>
-      </c>
-      <c r="F84" t="s">
-        <v>119</v>
-      </c>
-      <c r="G84" t="s">
-        <v>37</v>
-      </c>
-      <c r="H84" t="s">
-        <v>15</v>
-      </c>
-      <c r="I84" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B84" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
         <v>84</v>
       </c>
@@ -3268,16 +3327,16 @@
         <v>9</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>12</v>
+        <v>107</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>37</v>
@@ -3289,36 +3348,36 @@
         <v>12</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A86">
+    <row r="86" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="2">
         <v>85</v>
       </c>
-      <c r="B86" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" t="s">
-        <v>90</v>
-      </c>
-      <c r="D86" t="s">
-        <v>91</v>
-      </c>
-      <c r="E86" t="s">
-        <v>12</v>
-      </c>
-      <c r="F86" t="s">
-        <v>121</v>
-      </c>
-      <c r="G86" t="s">
-        <v>37</v>
-      </c>
-      <c r="H86" t="s">
-        <v>15</v>
-      </c>
-      <c r="I86" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B86" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
         <v>86</v>
       </c>
@@ -3326,29 +3385,928 @@
         <v>9</v>
       </c>
       <c r="C87" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I87" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="88" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="2">
+        <v>87</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="89" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="2">
+        <v>88</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="90" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="2">
+        <v>89</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="91" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="2">
         <v>90</v>
       </c>
-      <c r="D87" s="2" t="s">
+      <c r="B91" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="92" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="2">
         <v>91</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F87" s="2" t="s">
+      <c r="B92" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H92" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I92" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="2">
+        <v>92</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I93" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="2">
+        <v>93</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I94" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="2">
+        <v>94</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I95" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="2">
+        <v>95</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I96" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="2">
+        <v>96</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="2">
+        <v>97</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="2">
+        <v>98</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="2">
+        <v>99</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F100" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G87" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H87" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I87" s="2" t="s">
+      <c r="G100" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I100" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="2">
+        <v>100</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H101" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I101" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="2">
+        <v>101</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="2">
+        <v>102</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I103" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="2">
+        <v>103</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H104" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I104" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A105" s="2">
+        <v>104</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H105" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I105" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A106" s="2">
+        <v>105</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A107" s="2">
+        <v>106</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="2">
+        <v>107</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H108" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I108" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="2">
+        <v>108</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="2">
+        <v>109</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H110" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I110" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A111" s="2">
+        <v>110</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H111" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I111" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A112" s="2">
+        <v>111</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H112" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I112" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A113" s="2">
+        <v>112</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H113" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I113" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A114" s="2">
+        <v>113</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H114" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I114" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="2">
+        <v>114</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="2">
+        <v>115</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H116" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I116" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="2">
+        <v>116</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H117" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I117" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="2">
+        <v>117</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="H118" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I118" s="2" t="s">
         <v>12</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I1"/>
+  <autoFilter ref="A1:I118"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
@@ -3356,68 +4314,99 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="1" max="1" width="54" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>123</v>
+        <v>141</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B3" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="B4">
-        <v>86</v>
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="B6" s="4"/>
+        <v>145</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="B7">
-        <v>43</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B8">
-        <v>43</v>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B10" s="4"/>
+        <v>148</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>37</v>
       </c>
       <c r="B11">
-        <v>48</v>
+        <v>79</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3430,17 +4419,33 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="B13">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B15" s="4">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>150</v>
+      </c>
+      <c r="B15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>151</v>
+      </c>
+      <c r="B16">
         <v>7</v>
       </c>
     </row>

--- a/test-case-exports/Topup.xlsx
+++ b/test-case-exports/Topup.xlsx
@@ -443,7 +443,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-09-08T15:08:53.779Z</t>
+    <t>2026-09-09T06:44:10.265Z</t>
   </si>
   <si>
     <t>Total test cases</t>
